--- a/pages/research/papers/publications.xlsx
+++ b/pages/research/papers/publications.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="289">
   <si>
     <t xml:space="preserve">Section</t>
   </si>
@@ -473,6 +473,9 @@
   </si>
   <si>
     <t xml:space="preserve">XI SBSE - Simpósio Brasileiro de Sistemas Elétricos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.29327/1842969.1-325</t>
   </si>
   <si>
     <t xml:space="preserve">PACHECO, F. S. ; MAIA, THALES A. C. ; CASAS, F. L. ; EVANGELISTA, F. A.</t>
@@ -2407,7 +2410,9 @@
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
+      <c r="K31" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
@@ -2429,14 +2434,14 @@
         <v>142</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="2" t="s">
@@ -2467,14 +2472,14 @@
         <v>142</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="2" t="s">
@@ -2484,7 +2489,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
@@ -2507,24 +2512,24 @@
         <v>142</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
@@ -2539,7 +2544,7 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
       <c r="X34" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2547,24 +2552,24 @@
         <v>142</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
@@ -2579,7 +2584,7 @@
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
       <c r="X35" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2587,24 +2592,24 @@
         <v>142</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
@@ -2619,7 +2624,7 @@
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
       <c r="X36" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2627,24 +2632,24 @@
         <v>142</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
@@ -2659,7 +2664,7 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
       <c r="X37" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2667,18 +2672,18 @@
         <v>142</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -2697,7 +2702,7 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2705,18 +2710,18 @@
         <v>142</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -2735,7 +2740,7 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2743,18 +2748,18 @@
         <v>142</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
@@ -2773,7 +2778,7 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2781,18 +2786,18 @@
         <v>142</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -2811,7 +2816,7 @@
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
       <c r="X41" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2819,18 +2824,18 @@
         <v>142</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
@@ -2849,7 +2854,7 @@
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2857,18 +2862,18 @@
         <v>142</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
@@ -2887,7 +2892,7 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
       <c r="X43" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2895,18 +2900,18 @@
         <v>142</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
@@ -2925,7 +2930,7 @@
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
       <c r="X44" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2933,18 +2938,18 @@
         <v>142</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
@@ -2963,7 +2968,7 @@
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
       <c r="X45" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2971,24 +2976,24 @@
         <v>142</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
@@ -3003,7 +3008,7 @@
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
       <c r="X46" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3011,18 +3016,18 @@
         <v>142</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
@@ -3041,7 +3046,7 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
       <c r="X47" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3049,18 +3054,18 @@
         <v>142</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
@@ -3079,7 +3084,7 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3087,18 +3092,18 @@
         <v>142</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
@@ -3117,7 +3122,7 @@
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
       <c r="X49" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3125,18 +3130,18 @@
         <v>142</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
@@ -3155,7 +3160,7 @@
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
       <c r="X50" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3163,24 +3168,24 @@
         <v>142</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
@@ -3195,7 +3200,7 @@
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
       <c r="X51" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3203,18 +3208,18 @@
         <v>142</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -3233,7 +3238,7 @@
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3241,24 +3246,24 @@
         <v>142</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -3273,7 +3278,7 @@
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
       <c r="X53" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3281,24 +3286,24 @@
         <v>142</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
@@ -3313,7 +3318,7 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
       <c r="X54" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3321,24 +3326,24 @@
         <v>142</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -3353,7 +3358,7 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3361,24 +3366,24 @@
         <v>142</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
@@ -3393,7 +3398,7 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3401,24 +3406,24 @@
         <v>142</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
       <c r="K57" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
@@ -3433,7 +3438,7 @@
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
       <c r="X57" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3441,24 +3446,24 @@
         <v>142</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="D58" s="3"/>
       <c r="E58" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
       <c r="K58" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
@@ -3473,7 +3478,7 @@
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
       <c r="X58" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3481,24 +3486,24 @@
         <v>142</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="D59" s="3"/>
       <c r="E59" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
       <c r="K59" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
@@ -3513,7 +3518,7 @@
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
       <c r="X59" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3521,24 +3526,24 @@
         <v>142</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
       <c r="K60" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
@@ -3553,7 +3558,7 @@
       <c r="V60" s="3"/>
       <c r="W60" s="3"/>
       <c r="X60" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3561,24 +3566,24 @@
         <v>142</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="D61" s="3"/>
       <c r="E61" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
       <c r="K61" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
@@ -3593,7 +3598,7 @@
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
       <c r="X61" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3601,18 +3606,18 @@
         <v>142</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>2017</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
@@ -3631,7 +3636,7 @@
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>
       <c r="X62" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3639,18 +3644,18 @@
         <v>142</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>2015</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
@@ -3669,7 +3674,7 @@
       <c r="V63" s="3"/>
       <c r="W63" s="3"/>
       <c r="X63" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3677,18 +3682,18 @@
         <v>142</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>2013</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
@@ -3707,7 +3712,7 @@
       <c r="V64" s="3"/>
       <c r="W64" s="3"/>
       <c r="X64" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3715,18 +3720,18 @@
         <v>142</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>2012</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
@@ -3745,7 +3750,7 @@
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
       <c r="X65" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3753,24 +3758,24 @@
         <v>142</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>2011</v>
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
       <c r="K66" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
@@ -3785,7 +3790,7 @@
       <c r="V66" s="3"/>
       <c r="W66" s="3"/>
       <c r="X66" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3793,24 +3798,24 @@
         <v>142</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>2011</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
@@ -3825,7 +3830,7 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3833,18 +3838,18 @@
         <v>142</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>2012</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
@@ -3863,7 +3868,7 @@
       <c r="V68" s="3"/>
       <c r="W68" s="3"/>
       <c r="X68" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3871,18 +3876,18 @@
         <v>142</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>2011</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
@@ -3901,7 +3906,7 @@
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
       <c r="X69" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3909,18 +3914,18 @@
         <v>142</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>2010</v>
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
@@ -3939,7 +3944,7 @@
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
       <c r="X70" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3947,18 +3952,18 @@
         <v>142</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>2010</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
@@ -3977,7 +3982,7 @@
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
       <c r="X71" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3985,18 +3990,18 @@
         <v>142</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>2010</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
@@ -4015,7 +4020,7 @@
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
       <c r="X72" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4023,18 +4028,18 @@
         <v>142</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>2008</v>
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
@@ -4053,7 +4058,7 @@
       <c r="V73" s="3"/>
       <c r="W73" s="3"/>
       <c r="X73" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4061,18 +4066,18 @@
         <v>142</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>2007</v>
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
@@ -4091,7 +4096,7 @@
       <c r="V74" s="3"/>
       <c r="W74" s="3"/>
       <c r="X74" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
